--- a/output/pdf_financials_xlsx/IMM.xlsx
+++ b/output/pdf_financials_xlsx/IMM.xlsx
@@ -1393,19 +1393,19 @@
         <v>-0.113473</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.086113</v>
@@ -1721,19 +1721,19 @@
         <v>-0.113473</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.086113</v>
@@ -1922,19 +1922,19 @@
         <v>-0.113473</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.086113</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7.29</v>
+        <v>-7.29</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>7.830162</v>
+        <v>-7.830162</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>7.442412</v>
@@ -2216,19 +2216,19 @@
         <v>-0.113473</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.086113</v>
@@ -2350,19 +2350,19 @@
         <v>-0.113473</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.086113</v>
@@ -2514,19 +2514,19 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -6890,19 +6890,19 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.6109329999999999</v>
+        <v>0.64434</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.6109329999999999</v>
+        <v>0.626435</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.6109329999999999</v>
+        <v>0.626435</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0.6109329999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.934262</v>
+        <v>1.891217</v>
       </c>
       <c r="P92" s="3" t="n">
         <v>1.993809</v>
@@ -8589,28 +8589,28 @@
         <v>-0.190203</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.01275</v>
+        <v>-0.068846</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.0024</v>
+        <v>-0.064153</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.009825</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.239315</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.585024</v>
+        <v>0.554661</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0.040432</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.081427</v>
+        <v>-0.108133</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.135</v>
+        <v>0.05877</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>0</v>
@@ -12246,7 +12246,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13718,7 +13722,11 @@
           <t>Share-based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -25550,7 +25558,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -29574,7 +29586,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -52296,13 +52312,13 @@
         </is>
       </c>
       <c r="K404" s="5" t="n">
-        <v>0.036812</v>
+        <v>-0.036812</v>
       </c>
       <c r="L404" s="5" t="n">
-        <v>0.2916</v>
+        <v>-0.2916</v>
       </c>
       <c r="M404" s="5" t="n">
-        <v>0.626413</v>
+        <v>-0.626413</v>
       </c>
       <c r="N404" t="inlineStr">
         <is>
@@ -53232,10 +53248,10 @@
         </is>
       </c>
       <c r="I413" s="5" t="n">
-        <v>0.329208</v>
+        <v>-0.329208</v>
       </c>
       <c r="J413" s="5" t="n">
-        <v>0.233912</v>
+        <v>-0.233912</v>
       </c>
       <c r="K413" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/IMM.xlsx
+++ b/output/pdf_financials_xlsx/IMM.xlsx
@@ -1125,16 +1125,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001109</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000309</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000106</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-6e-06</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2216,16 +2216,16 @@
         <v>-0.113473</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.329208</v>
+        <v>-0.328099</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.233912</v>
+        <v>-0.233603</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.036812</v>
+        <v>-0.036706</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.2916</v>
+        <v>-0.291594</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.626413</v>
@@ -2350,16 +2350,16 @@
         <v>-0.113473</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.329208</v>
+        <v>-0.328099</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.233912</v>
+        <v>-0.233603</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.036812</v>
+        <v>-0.036706</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.2916</v>
+        <v>-0.291594</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.626413</v>
@@ -2702,31 +2702,31 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006344</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003272</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000793</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.011609</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.13184</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003983</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.029854</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.009348</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.002576</v>
       </c>
     </row>
     <row r="35">
@@ -2842,31 +2842,31 @@
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006344</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003272</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000793</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.011609</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.13184</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.003983</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.029854</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.009348</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.002576</v>
       </c>
     </row>
     <row r="37">
@@ -3690,31 +3690,31 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.912431</v>
+        <v>0.906087</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.474604</v>
+        <v>0.471332</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.682803</v>
+        <v>0.68201</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.971391</v>
+        <v>0.959782</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.5881420000000001</v>
+        <v>0.456302</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.027185</v>
+        <v>0.023202</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.044249</v>
+        <v>0.014395</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.080912</v>
+        <v>0.071564</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.003576</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="49">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11604,7 +11604,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -12680,7 +12684,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -19770,7 +19774,11 @@
           <t>Loss on write-off of reclamation deposit</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -24086,7 +24094,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -40218,7 +40230,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -51754,7 +51766,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
